--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121237954</v>
       </c>
       <c r="B4" t="n">
-        <v>91237</v>
+        <v>91247</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>121241213</v>
       </c>
       <c r="B27" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121237954</v>
       </c>
       <c r="B4" t="n">
-        <v>91247</v>
+        <v>91259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>121241213</v>
       </c>
       <c r="B27" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121237954</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>91260</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>121241213</v>
       </c>
       <c r="B27" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121237954</v>
       </c>
       <c r="B4" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>121241213</v>
       </c>
       <c r="B27" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121237954</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>91269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>121241213</v>
       </c>
       <c r="B27" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>121237954</v>
       </c>
       <c r="B4" t="n">
-        <v>91269</v>
+        <v>91270</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3623,7 +3623,7 @@
         <v>121241213</v>
       </c>
       <c r="B27" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112275278</v>
+        <v>16596148</v>
       </c>
       <c r="B2" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646126</v>
+        <v>646475</v>
       </c>
       <c r="R2" t="n">
-        <v>6568636</v>
+        <v>6569002</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,56 +786,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112275279</v>
+        <v>16693705</v>
       </c>
       <c r="B3" t="n">
-        <v>90873</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Larslund, 125 m NNO om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646126</v>
+        <v>646480</v>
       </c>
       <c r="R3" t="n">
-        <v>6568636</v>
+        <v>6568994</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,12 +860,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,13 +874,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>mossrik barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -893,53 +897,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121237954</v>
+        <v>16693436</v>
       </c>
       <c r="B4" t="n">
-        <v>91270</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3884</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sandsborg, Srm</t>
+          <t>Naturskolan, V om Kiholm, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646130</v>
+        <v>646288</v>
       </c>
       <c r="R4" t="n">
-        <v>6568421</v>
+        <v>6568443</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,69 +978,88 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>aspskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>16596333</v>
+        <v>128579912</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Larslund, 200 m SV om, Srm</t>
+          <t>Lina vid Naturskolan, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>646345.7756120953</v>
+        <v>646307</v>
       </c>
       <c r="R5" t="n">
-        <v>6568796.00882252</v>
+        <v>6568454</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1083,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,13 +1097,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1116,16 +1123,11 @@
         <v>16596549</v>
       </c>
       <c r="B6" t="n">
-        <v>90655</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1153,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>646473.9076076892</v>
+        <v>646474</v>
       </c>
       <c r="R6" t="n">
-        <v>6568986.364413029</v>
+        <v>6568986</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1186,19 +1188,9 @@
           <t>2014-09-17</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,50 +1222,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16596598</v>
+        <v>112275250</v>
       </c>
       <c r="B7" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>1106</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646473.9076076892</v>
+        <v>646166</v>
       </c>
       <c r="R7" t="n">
-        <v>6568986.364413029</v>
+        <v>6568529</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1300,22 +1287,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,13 +1301,22 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>gammal barrskog</t>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1348,15 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16596570</v>
+        <v>121241213</v>
       </c>
       <c r="B8" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1364,46 +1345,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Larslund, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646459.877114721</v>
+        <v>646322</v>
       </c>
       <c r="R8" t="n">
-        <v>6568950.994031222</v>
+        <v>6568869</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,22 +1399,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,36 +1415,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16596269</v>
+        <v>16596581</v>
       </c>
       <c r="B9" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,34 +1442,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Larslund, 200 m SV om, Srm</t>
+          <t>Larslund strax N om, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646345.7756120953</v>
+        <v>646434</v>
       </c>
       <c r="R9" t="n">
-        <v>6568796.00882252</v>
+        <v>6568901</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1547,21 +1508,11 @@
           <t>2014-09-17</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2014-09-17</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1573,7 +1524,17 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>barrskog</t>
+          <t>gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1591,50 +1552,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16596147</v>
+        <v>73563665</v>
       </c>
       <c r="B10" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1968</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Larslund, 100 m NO om, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646541.2618779155</v>
+        <v>646207</v>
       </c>
       <c r="R10" t="n">
-        <v>6568942.861672431</v>
+        <v>6568477</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,22 +1619,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,38 +1633,44 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>gammal tallskog</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16596537</v>
+        <v>16596147</v>
       </c>
       <c r="B11" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1724,34 +1678,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>1968</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Larslund, 100 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>646478.5383970508</v>
+        <v>646541</v>
       </c>
       <c r="R11" t="n">
-        <v>6568999.347842662</v>
+        <v>6568943</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1781,21 +1735,11 @@
           <t>2014-09-17</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2014-09-17</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1807,7 +1751,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>bergig tallskog</t>
+          <t>gammal tallskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1825,37 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16596560</v>
+        <v>16596558</v>
       </c>
       <c r="B12" t="n">
-        <v>90671</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4368</v>
+        <v>2180</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1865,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>646447.935585688</v>
+        <v>646474</v>
       </c>
       <c r="R12" t="n">
-        <v>6568967.948957363</v>
+        <v>6568986</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1898,19 +1837,9 @@
           <t>2014-09-17</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1942,62 +1871,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16596148</v>
+        <v>121237954</v>
       </c>
       <c r="B13" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>3884</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Larslund 150 m N om, Srm</t>
+          <t>Sandsborg, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>646475.3461115662</v>
+        <v>646130</v>
       </c>
       <c r="R13" t="n">
-        <v>6569002.298039754</v>
+        <v>6568421</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2021,22 +1936,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,71 +1952,70 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16596558</v>
+        <v>16596570</v>
       </c>
       <c r="B14" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2180</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>646473.9076076892</v>
+        <v>646460</v>
       </c>
       <c r="R14" t="n">
-        <v>6568986.364413029</v>
+        <v>6568951</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2141,19 +2045,9 @@
           <t>2014-09-17</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2014-09-17</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,15 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16693050</v>
+        <v>16596269</v>
       </c>
       <c r="B15" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,46 +2090,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
+          <t>Larslund, 200 m SV om, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>646148.4924872008</v>
+        <v>646346</v>
       </c>
       <c r="R15" t="n">
-        <v>6568775.614403469</v>
+        <v>6568796</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2264,22 +2144,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,7 +2163,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>hällmarkstallskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2311,15 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16693067</v>
+        <v>16693358</v>
       </c>
       <c r="B16" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2327,34 +2192,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
+          <t>Naturskolan, V om Kiholm, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>646148.4924872008</v>
+        <v>646255</v>
       </c>
       <c r="R16" t="n">
-        <v>6568775.614403469</v>
+        <v>6568522</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2384,21 +2249,11 @@
           <t>2014-09-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2014-09-30</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2410,7 +2265,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>hällmarkstallskog</t>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2428,59 +2283,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16693705</v>
+        <v>16693727</v>
       </c>
       <c r="B17" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>4366</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Larslund, 125 m NNO om, Srm</t>
+          <t>Larslund, 150 m NNO om, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>646479.7601419021</v>
+        <v>646495</v>
       </c>
       <c r="R17" t="n">
-        <v>6568994.272918969</v>
+        <v>6568996</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,19 +2351,9 @@
           <t>2014-09-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,50 +2385,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16693883</v>
+        <v>16596560</v>
       </c>
       <c r="B18" t="n">
-        <v>88921</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5741</v>
+        <v>4368</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Larslund, 150 m NO - NNO om, Srm</t>
+          <t>Larslund 150 m N om, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>646551.0159830885</v>
+        <v>646448</v>
       </c>
       <c r="R18" t="n">
-        <v>6568956.042841134</v>
+        <v>6568968</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2624,22 +2450,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,7 +2469,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>mossrik barrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2671,50 +2487,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16693358</v>
+        <v>112275279</v>
       </c>
       <c r="B19" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4368</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Naturskolan, V om Kiholm, Srm</t>
+          <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>646255.2466745003</v>
+        <v>646126</v>
       </c>
       <c r="R19" t="n">
-        <v>6568521.54892104</v>
+        <v>6568636</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2741,22 +2555,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2765,12 +2569,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>blandskog</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2788,15 +2593,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16693727</v>
+        <v>128579897</v>
       </c>
       <c r="B20" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,37 +2604,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>4379</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Larslund, 150 m NNO om, Srm</t>
+          <t>Lina vid Naturskolan, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>646494.5589568611</v>
+        <v>646307</v>
       </c>
       <c r="R20" t="n">
-        <v>6568996.379754236</v>
+        <v>6568454</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2858,22 +2658,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,7 +2677,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>mossrik barrskog</t>
+          <t>blandskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2905,62 +2695,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16693735</v>
+        <v>104721941</v>
       </c>
       <c r="B21" t="n">
-        <v>90656</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6003297</v>
+        <v>4405</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Pers.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Larslund, 150 m NNO om, Srm</t>
+          <t>Södertälje naturskola, strax V om, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>646494.5589568611</v>
+        <v>646196</v>
       </c>
       <c r="R21" t="n">
-        <v>6568996.379754236</v>
+        <v>6568413</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2984,22 +2760,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-09-30</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3013,7 +2779,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>mossrik barrskog</t>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3031,50 +2797,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16693754</v>
+        <v>16693067</v>
       </c>
       <c r="B22" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>4745</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Larslund, 75 m NO om, Srm</t>
+          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>646502.2642445986</v>
+        <v>646148</v>
       </c>
       <c r="R22" t="n">
-        <v>6568929.577880156</v>
+        <v>6568776</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3104,34 +2865,23 @@
           <t>2014-09-30</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2014-09-30</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>mossrik barrskog</t>
+          <t>hällmarkstallskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3149,55 +2899,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>73563665</v>
+        <v>112275263</v>
       </c>
       <c r="B23" t="n">
-        <v>90005</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1339</v>
+        <v>5448</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Naturskoleskogen, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>646206.6633416803</v>
+        <v>646200</v>
       </c>
       <c r="R23" t="n">
-        <v>6568477.16263372</v>
+        <v>6568598</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3221,22 +2964,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3245,87 +2978,71 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104721941</v>
+        <v>16596577</v>
       </c>
       <c r="B24" t="n">
-        <v>86196</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4405</v>
+        <v>5741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Södertälje naturskola, strax V om, Srm</t>
+          <t>Larslund strax N om, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>646195.7792996226</v>
+        <v>646434</v>
       </c>
       <c r="R24" t="n">
-        <v>6568413.222641654</v>
+        <v>6568901</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3349,22 +3066,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-10-22</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3378,7 +3085,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3396,15 +3103,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112275263</v>
+        <v>16693675</v>
       </c>
       <c r="B25" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3412,37 +3114,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5448</v>
+        <v>5741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>V om Kiholm, 250 m NNO om Naturskolan, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>646200</v>
+        <v>646388</v>
       </c>
       <c r="R25" t="n">
-        <v>6568598</v>
+        <v>6568743</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3466,12 +3168,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3485,7 +3187,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3503,50 +3205,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112275250</v>
+        <v>16693883</v>
       </c>
       <c r="B26" t="n">
-        <v>89857</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1106</v>
+        <v>5741</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Naturskoleskogen, Srm</t>
+          <t>Larslund, 150 m NO - NNO om, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>646166</v>
+        <v>646551</v>
       </c>
       <c r="R26" t="n">
-        <v>6568529</v>
+        <v>6568956</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3573,12 +3270,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2014-09-30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3592,17 +3289,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>mossrik barrskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3620,53 +3307,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121241213</v>
+        <v>128579902</v>
       </c>
       <c r="B27" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5836</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Larslund, Srm</t>
+          <t>Lina vid Naturskolan, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>646322</v>
+        <v>646307</v>
       </c>
       <c r="R27" t="n">
-        <v>6568869</v>
+        <v>6568454</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3690,12 +3372,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,19 +3388,1199 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>16596333</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Larslund, 200 m SV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>646346</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6568796</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16596598</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Larslund 150 m N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>646474</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6568986</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16596615</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Larslund strax N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>646434</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6568901</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16693754</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Larslund, 75 m NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>646502</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6568930</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>mossrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>16596537</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Larslund 150 m N om, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>646479</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6568999</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2014-09-17</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>bergig tallskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>16692991</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>V om Kiholm, 250 m NV om Södertälje naturskola, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>646137</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6568725</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Olikåldrig barrskog med björkinslag</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>16693027</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>V om Kiholm, 550 m NNV om Södertälje naturskola, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>646145</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6568972</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ytterenhörna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>bergig barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>16693050</v>
+      </c>
+      <c r="B35" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>V om Kiholm, 350 m NV om Södertälje naturskola, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>646148</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6568776</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>hällmarkstallskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>112275278</v>
+      </c>
+      <c r="B36" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Naturskoleskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>646126</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6568636</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>102014138</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lina 12, Södertälje, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>646368</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6568735</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-07-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På stigen, gränsen mellan Underås och Dammkärr</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>16693735</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93200</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6003297</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spricktaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Larslund, 150 m NNO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>646495</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6568996</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>mossrik barrskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59863-2022 artfynd.xlsx
+++ b/artfynd/A 59863-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596148</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693705</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693436</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128579912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596549</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112275250</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121241213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596581</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73563665</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596147</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596558</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121237954</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2076,6 +2141,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596570</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596269</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693358</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2382,6 +2462,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693727</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2484,6 +2569,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596560</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,6 +2680,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112275279</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2692,6 +2787,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128579897</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2794,6 +2894,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104721941</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +3001,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693067</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2998,6 +3108,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112275263</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3100,6 +3215,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596577</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3202,6 +3322,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693675</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3304,6 +3429,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693883</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3406,6 +3536,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128579902</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3509,6 +3644,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596333</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3612,6 +3752,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596598</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3715,6 +3860,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596615</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3818,6 +3968,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693754</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3920,6 +4075,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16596537</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4031,6 +4191,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16692991</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4142,6 +4307,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693027</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4253,6 +4423,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693050</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4355,6 +4530,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112275278</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4470,6 +4650,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102014138</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4581,8 +4766,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16693735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>